--- a/forms/trg/Formulir_TRG_nms-rg.xlsx
+++ b/forms/trg/Formulir_TRG_nms-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Abdullah Sanusi, S.E., M.B.A., Ph.D.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Universitas Hasanuddin</t>
@@ -959,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1074,7 +1078,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1115,7 +1119,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1144,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
